--- a/benchmark/resource/models_list.xlsx
+++ b/benchmark/resource/models_list.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10420"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10212"/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/maxy/Documents/pythonProject/my_experiemnt/model-level-testing/DeepEval/benchmark/DeepEval/resource/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/maxy/Documents/文档资料/个人资料/我的成果/DeepEval-artifacts/source_code/DeepEval_DeepEval/DeepEval/benchmark/resource/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06C5BA86-A9E6-FE48-BE77-8456C41148C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAFD2E9B-1E71-F34C-A2BD-95598F2763A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5080" yWindow="-13900" windowWidth="21960" windowHeight="13900" xr2:uid="{649F85AB-6F99-0242-B559-A02AF107F89E}"/>
+    <workbookView xWindow="1440" yWindow="-13900" windowWidth="25600" windowHeight="13900" xr2:uid="{649F85AB-6F99-0242-B559-A02AF107F89E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,6 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -36,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="90">
   <si>
     <t>LeNet-5</t>
   </si>
@@ -244,6 +243,89 @@
   </si>
   <si>
     <t>Category</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Proceedings of the IEEE</t>
+  </si>
+  <si>
+    <t>Proceedings of the IEEE Conference on Computer Vision and Pattern Recognition</t>
+  </si>
+  <si>
+    <t>https://arxiv.org/abs/1409.1556</t>
+  </si>
+  <si>
+    <t>International Conference on Learning Representations</t>
+  </si>
+  <si>
+    <t>https://arxiv.org/abs/1605.07146</t>
+  </si>
+  <si>
+    <t>https://arxiv.org/abs/1609.05672</t>
+  </si>
+  <si>
+    <t>IEEE Transactions on Pattern Analysis and Machine Intelligence</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>IEEE Transactions on Circuits and Systems for Video Technology </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Proceedings of the European Conference on Computer Vision</t>
+  </si>
+  <si>
+    <t>IEEE Access</t>
+  </si>
+  <si>
+    <t>https://arxiv.org/abs/1704.04861</t>
+  </si>
+  <si>
+    <t>Proceedings of the IEEE/CVF International Conference on Computer Vision</t>
+  </si>
+  <si>
+    <t>Proceedings of the European Conference on Computer Vision </t>
+  </si>
+  <si>
+    <t>Proceedings of the AAAI Conference on Artificial Intelligence</t>
+  </si>
+  <si>
+    <t>http://arxiv.org/abs/1602.07360</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Proceedings of the IEEE/CVF International Conference on Computer Vision </t>
+  </si>
+  <si>
+    <t>https://arxiv.org/abs/1312.4400</t>
+  </si>
+  <si>
+    <t>https://arxiv.org/abs/1806.00178</t>
+  </si>
+  <si>
+    <t>https://arxiv.org/abs/1907.09595</t>
+  </si>
+  <si>
+    <t>European Conference on Computer Vision</t>
+  </si>
+  <si>
+    <t>Proceedings of the 36th International Conference on Machine Learning</t>
+  </si>
+  <si>
+    <t>Neural computation</t>
+  </si>
+  <si>
+    <t>2017 IEEE 60th international midwest symposium on circuits and systems</t>
+  </si>
+  <si>
+    <t>IEEE transactions on Signal Processing</t>
+  </si>
+  <si>
+    <t>Publications</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Years</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -344,11 +426,13 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
       <right style="thin">
         <color auto="1"/>
       </right>
-      <top style="thin">
+      <top style="slantDashDot">
         <color auto="1"/>
       </top>
       <bottom style="thin">
@@ -362,11 +446,10 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -379,18 +462,24 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -420,39 +509,39 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="0E2841"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E8E8E8"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="156082"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="E97132"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="196B24"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="0F9ED5"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="A02B93"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="4EA72E"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="467886"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="96607D"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -504,7 +593,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -615,6 +704,13 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
@@ -623,13 +719,6 @@
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -694,31 +783,11 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -729,588 +798,885 @@
   <dimension ref="A1:E51"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="24.33203125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="33.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="70.83203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.33203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="31.6640625" customWidth="1"/>
+    <col min="3" max="3" width="29" customWidth="1"/>
+    <col min="4" max="4" width="28.33203125" customWidth="1"/>
+    <col min="5" max="5" width="9.33203125" style="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="D1" s="8"/>
+      <c r="D1" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="C2" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="D2" s="1"/>
+      <c r="C2" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2" s="10">
+        <v>1998</v>
+      </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="C3" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="D3" s="1"/>
+      <c r="C3" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="E3" s="10">
+        <v>2016</v>
+      </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="C4" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
+      <c r="C4" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="E4" s="10">
+        <v>2014</v>
+      </c>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="C5" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
+      <c r="C5" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="E5" s="10">
+        <v>2014</v>
+      </c>
     </row>
     <row r="6" spans="1:5" ht="17" customHeight="1">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="C6" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
+      <c r="D6" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="E6" s="10">
+        <v>2016</v>
+      </c>
     </row>
     <row r="7" spans="1:5" ht="17" customHeight="1">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B7" s="10" t="s">
+      <c r="B7" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="C7" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="D7" s="1"/>
+      <c r="D7" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="E7" s="10">
+        <v>2017</v>
+      </c>
     </row>
     <row r="8" spans="1:5" ht="17" customHeight="1">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B8" s="10" t="s">
+      <c r="B8" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="C8" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="D8" s="1"/>
+      <c r="D8" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="E8" s="10">
+        <v>2017</v>
+      </c>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B9" s="10" t="s">
+      <c r="B9" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="C9" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="D9" s="1"/>
+      <c r="D9" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="E9" s="10">
+        <v>2017</v>
+      </c>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B10" s="10" t="s">
+      <c r="B10" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="C10" s="10" t="s">
+      <c r="C10" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="D10" s="1"/>
+      <c r="D10" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="E10" s="10">
+        <v>2021</v>
+      </c>
     </row>
     <row r="11" spans="1:5" ht="17" customHeight="1">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B11" s="10" t="s">
+      <c r="B11" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="C11" s="10" t="s">
+      <c r="C11" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="D11" s="1"/>
+      <c r="D11" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="E11" s="10">
+        <v>2018</v>
+      </c>
     </row>
     <row r="12" spans="1:5" ht="17" customHeight="1">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B12" s="10" t="s">
+      <c r="B12" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="C12" s="10" t="s">
-        <v>55</v>
+      <c r="C12" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="E12" s="10">
+        <v>2018</v>
       </c>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B13" s="9" t="s">
+      <c r="B13" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="C13" s="9" t="s">
-        <v>55</v>
+      <c r="C13" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="E13" s="10">
+        <v>2017</v>
       </c>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B14" s="9" t="s">
+      <c r="B14" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="C14" s="9" t="s">
-        <v>55</v>
+      <c r="C14" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="E14" s="10">
+        <v>2017</v>
       </c>
     </row>
     <row r="15" spans="1:5">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B15" s="9" t="s">
+      <c r="B15" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="C15" s="9" t="s">
-        <v>55</v>
+      <c r="C15" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="E15" s="10">
+        <v>2018</v>
       </c>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B16" s="9" t="s">
+      <c r="B16" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="C16" s="9" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" s="3" t="s">
+      <c r="C16" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="E16" s="10">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B17" s="9" t="s">
+      <c r="B17" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="C17" s="9" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" s="3" t="s">
+      <c r="C17" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="E17" s="10">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B18" s="10" t="s">
+      <c r="B18" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="C18" s="10" t="s">
+      <c r="C18" s="8" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" s="3" t="s">
+      <c r="D18" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="E18" s="10">
+        <v>2017</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B19" s="10" t="s">
+      <c r="B19" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="C19" s="10" t="s">
+      <c r="C19" s="8" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" s="3" t="s">
+      <c r="D19" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="E19" s="10">
+        <v>2018</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B20" s="10" t="s">
+      <c r="B20" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="C20" s="10" t="s">
+      <c r="C20" s="8" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" ht="17" customHeight="1">
-      <c r="A21" s="3" t="s">
+      <c r="D20" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E20" s="10">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="17" customHeight="1">
+      <c r="A21" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B21" s="10" t="s">
+      <c r="B21" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="C21" s="10" t="s">
+      <c r="C21" s="8" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" ht="17" customHeight="1">
-      <c r="A22" s="3" t="s">
+      <c r="D21" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="E21" s="10">
+        <v>2018</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="17" customHeight="1">
+      <c r="A22" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B22" s="10" t="s">
+      <c r="B22" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="C22" s="10" t="s">
+      <c r="C22" s="8" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" ht="17" customHeight="1">
-      <c r="A23" s="3" t="s">
+      <c r="D22" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="E22" s="10">
+        <v>2018</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="17" customHeight="1">
+      <c r="A23" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B23" s="10" t="s">
+      <c r="B23" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="C23" s="10" t="s">
+      <c r="C23" s="8" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" ht="17" customHeight="1">
-      <c r="A24" s="3" t="s">
+      <c r="D23" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="E23" s="10">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="17" customHeight="1">
+      <c r="A24" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B24" s="10" t="s">
+      <c r="B24" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="C24" s="10" t="s">
+      <c r="C24" s="8" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" ht="17" customHeight="1">
-      <c r="A25" s="3" t="s">
+      <c r="D24" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="E24" s="10">
+        <v>2016</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="17" customHeight="1">
+      <c r="A25" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B25" s="10" t="s">
+      <c r="B25" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="C25" s="10" t="s">
+      <c r="C25" s="8" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" ht="17" customHeight="1">
-      <c r="A26" s="3" t="s">
+      <c r="D25" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="E25" s="10">
+        <v>2016</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="17" customHeight="1">
+      <c r="A26" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B26" s="10" t="s">
+      <c r="B26" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="C26" s="10" t="s">
+      <c r="C26" s="8" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="27" spans="1:3" ht="17" customHeight="1">
-      <c r="A27" s="3" t="s">
+      <c r="D26" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="E26" s="10">
+        <v>2017</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="17" customHeight="1">
+      <c r="A27" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B27" s="10" t="s">
+      <c r="B27" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="C27" s="10" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" ht="17" customHeight="1">
-      <c r="A28" s="3" t="s">
+      <c r="C27" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="E27" s="10">
+        <v>2017</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="17" customHeight="1">
+      <c r="A28" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B28" s="10" t="s">
+      <c r="B28" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="C28" s="10" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3">
-      <c r="A29" s="3" t="s">
+      <c r="C28" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="E28" s="10">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B29" s="10" t="s">
+      <c r="B29" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="C29" s="10" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" ht="17" customHeight="1">
-      <c r="A30" s="3" t="s">
+      <c r="C29" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="E29" s="10">
+        <v>2017</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="17" customHeight="1">
+      <c r="A30" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B30" s="10" t="s">
+      <c r="B30" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="C30" s="10" t="s">
+      <c r="C30" s="8" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="31" spans="1:3">
-      <c r="A31" s="3" t="s">
+      <c r="D30" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="E30" s="10">
+        <v>2016</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B31" s="10" t="s">
+      <c r="B31" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="C31" s="10" t="s">
+      <c r="C31" s="8" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="32" spans="1:3" ht="17" customHeight="1">
-      <c r="A32" s="3" t="s">
+      <c r="D31" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="E31" s="10">
+        <v>2018</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="17" customHeight="1">
+      <c r="A32" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B32" s="10" t="s">
+      <c r="B32" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="C32" s="10" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3">
-      <c r="A33" s="4" t="s">
+      <c r="C32" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="E32" s="10">
+        <v>2018</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B33" s="10" t="s">
+      <c r="B33" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="C33" s="10" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3">
-      <c r="A34" s="4" t="s">
+      <c r="C33" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="E33" s="10">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B34" s="10" t="s">
+      <c r="B34" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="C34" s="10" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3">
-      <c r="A35" s="3" t="s">
+      <c r="C34" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="D34" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="E34" s="10">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B35" s="10" t="s">
+      <c r="B35" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="C35" s="10" t="s">
+      <c r="C35" s="8" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="36" spans="1:3">
-      <c r="A36" s="3" t="s">
+      <c r="D35" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="E35" s="10">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B36" s="10" t="s">
+      <c r="B36" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="C36" s="10" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" ht="17" customHeight="1">
-      <c r="A37" s="5" t="s">
+      <c r="C36" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="D36" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="E36" s="10">
+        <v>2014</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="17" customHeight="1">
+      <c r="A37" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="B37" s="10" t="s">
+      <c r="B37" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="C37" s="10" t="s">
+      <c r="C37" s="8" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="38" spans="1:3" ht="17" customHeight="1">
-      <c r="A38" s="5" t="s">
+      <c r="D37" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="E37" s="10">
+        <v>2018</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" ht="17" customHeight="1">
+      <c r="A38" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B38" s="10" t="s">
+      <c r="B38" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="C38" s="10" t="s">
+      <c r="C38" s="8" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="39" spans="1:3" ht="17" customHeight="1">
-      <c r="A39" s="5" t="s">
+      <c r="D38" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="E38" s="10">
+        <v>2018</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" ht="17" customHeight="1">
+      <c r="A39" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="B39" s="10" t="s">
+      <c r="B39" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="C39" s="10" t="s">
+      <c r="C39" s="8" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="40" spans="1:3" ht="17" customHeight="1">
-      <c r="A40" s="3" t="s">
+      <c r="D39" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="E39" s="10">
+        <v>2018</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" ht="17" customHeight="1">
+      <c r="A40" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B40" s="10" t="s">
+      <c r="B40" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="C40" s="10" t="s">
+      <c r="C40" s="8" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="41" spans="1:3" ht="17" customHeight="1">
-      <c r="A41" s="3" t="s">
+      <c r="D40" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="E40" s="10">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" ht="17" customHeight="1">
+      <c r="A41" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B41" s="10" t="s">
+      <c r="B41" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="C41" s="10" t="s">
+      <c r="C41" s="8" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="42" spans="1:3">
-      <c r="A42" s="3" t="s">
+      <c r="D41" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="E41" s="10">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B42" s="10" t="s">
+      <c r="B42" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="C42" s="10" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3">
-      <c r="A43" s="3" t="s">
+      <c r="C42" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="D42" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="E42" s="10">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B43" s="10" t="s">
+      <c r="B43" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="C43" s="10" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3">
-      <c r="A44" s="3" t="s">
+      <c r="C43" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="D43" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="E43" s="10">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B44" s="9" t="s">
+      <c r="B44" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="C44" s="9" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" ht="17" customHeight="1">
-      <c r="A45" s="3" t="s">
+      <c r="C44" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D44" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="E44" s="10">
+        <v>2014</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" ht="17" customHeight="1">
+      <c r="A45" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B45" s="10" t="s">
+      <c r="B45" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="C45" s="10" t="s">
+      <c r="C45" s="8" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="46" spans="1:3">
-      <c r="A46" s="3" t="s">
+      <c r="D45" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="E45" s="10">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B46" s="10" t="s">
+      <c r="B46" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="C46" s="10" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3">
-      <c r="A47" s="3" t="s">
+      <c r="C46" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="D46" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="E46" s="10">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B47" s="10" t="s">
+      <c r="B47" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="C47" s="10" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3">
-      <c r="A48" s="3" t="s">
+      <c r="C47" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="D47" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="E47" s="10">
+        <v>2018</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="B48" s="9" t="s">
+      <c r="B48" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="C48" s="9" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3">
-      <c r="A49" s="3" t="s">
+      <c r="C48" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D48" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="E48" s="10">
+        <v>2018</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B49" s="10" t="s">
+      <c r="B49" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="C49" s="10" t="s">
+      <c r="C49" s="8" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="50" spans="1:3">
-      <c r="A50" s="3" t="s">
+      <c r="D49" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="E49" s="10">
+        <v>1997</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B50" s="10" t="s">
+      <c r="B50" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="C50" s="10" t="s">
+      <c r="C50" s="8" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="51" spans="1:3">
-      <c r="A51" s="3" t="s">
+      <c r="D50" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="E50" s="10">
+        <v>2017</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B51" s="10" t="s">
+      <c r="B51" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="C51" s="10" t="s">
+      <c r="C51" s="8" t="s">
         <v>57</v>
+      </c>
+      <c r="D51" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="E51" s="10">
+        <v>1997</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="D30" r:id="rId1" xr:uid="{114F9A9D-C751-674D-BF60-2572457BA162}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>